--- a/excel_lotto_records/lotto_megamil.xlsx
+++ b/excel_lotto_records/lotto_megamil.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,31 +413,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Numbers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MP</t>
         </is>
@@ -35995,6 +35983,44 @@
         <v>8</v>
       </c>
       <c r="E1746" t="inlineStr"/>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="n">
+        <v>1745</v>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>10/13/2026</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>11-12-15-40-66</t>
+        </is>
+      </c>
+      <c r="D1747" t="n">
+        <v>17</v>
+      </c>
+      <c r="E1747" t="inlineStr"/>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="n">
+        <v>1746</v>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>10/16/2026</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>2-15-31-41-68</t>
+        </is>
+      </c>
+      <c r="D1748" t="n">
+        <v>11</v>
+      </c>
+      <c r="E1748" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
